--- a/PMI/Sinops/phase2-detail-design/DD/Sinops_IFレイアウト_発注勧告.xlsx
+++ b/PMI/Sinops/phase2-detail-design/DD/Sinops_IFレイアウト_発注勧告.xlsx
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C13" s="60" t="inlineStr">
         <is>
-          <t>Layer① STEP20 採用判定</t>
+          <t>Layer① STEP40 採用判定</t>
         </is>
       </c>
       <c r="D13" s="60" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="F13" s="60" t="inlineStr">
         <is>
-          <t>当日を不採用とし、昨日の翌日以降を 1 本として採用して STEP30 へ</t>
+          <t>当日を不採用とし、昨日の翌日以降を 1 本として採用して STEP50 へ</t>
         </is>
       </c>
       <c r="G13" s="60" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>02 STEP20</t>
+          <t>02 STEP40</t>
         </is>
       </c>
       <c r="F17" s="58" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="I18" s="58" t="inlineStr">
         <is>
-          <t>Layer① は 24/25 共通 1 ジョブ。STEP20 で 1 本採用。Layer③ は kankoku_* と subkankoku_* を毎日出力。締切は TBD-19</t>
+          <t>Layer① は 24/25 共通 1 ジョブ。STEP40 で 1 本採用。Layer③ は kankoku_* と subkankoku_* を毎日出力。締切は TBD-19</t>
         </is>
       </c>
       <c r="J18" s="58" t="inlineStr">
@@ -8766,7 +8766,7 @@
     <row r="2" ht="42" customHeight="1" s="65">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Layer③ は当日・翌日以降を毎日出力。Layer① は 24/25 共通 1 ジョブで 1 本を採用（判定は 02 STEP20）</t>
+          <t>Layer③ は当日・翌日以降を毎日出力。Layer① は 24/25 共通 1 ジョブで 1 本を採用（判定は 02 STEP40）</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H32"/>
+  <dimension ref="B1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="2" customWidth="1" style="65" min="1" max="1"/>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="C6" s="60" t="inlineStr">
         <is>
-          <t>当日 kankoku_* と昨日の subkankoku_* をプル。STEP20 で 1 本を採用し、SIREJAN_RCMDORDER_LAST（7項目）へ変換。自動発注GCSへ SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss。24/25 共通 1 ジョブ。2本は重ねない</t>
+          <t>当日 kankoku_* と昨日の subkankoku_* をプル。STEP40 で 1 本を採用し、SIREJAN_RCMDORDER_LAST（7項目）へ変換。自動発注GCSへ SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss。24/25 共通 1 ジョブ。2本は重ねない</t>
         </is>
       </c>
       <c r="D6" s="69" t="n"/>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="C8" s="60" t="inlineStr">
         <is>
-          <t>STEP20。指定時刻（TBD-19、例 6:00）までに当日作成済 → 当日。障害または未作成 → 昨日の翌日以降。2本は重ねない</t>
+          <t>STEP40。指定時刻（TBD-19、例 6:00）までに当日作成済 → 当日。障害または未作成 → 昨日の翌日以降。2本は重ねない</t>
         </is>
       </c>
       <c r="D8" s="69" t="n"/>
@@ -11819,229 +11819,541 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1" s="65">
-      <c r="B16" s="60" t="n">
-        <v>10</v>
+    <row r="16" ht="18" customHeight="1" s="65">
+      <c r="B16" s="60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>kankoku.end / subkankoku.end を確認してから gz を取得・展開し、クラウド機へステージング</t>
+          <t>.end を確認</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr">
         <is>
-          <t>gs://ods-seiyu-prod/{TBD-05}/ 当日 ＋ 昨日の翌日以降</t>
+          <t>kankoku.end / subkankoku.end</t>
         </is>
       </c>
       <c r="E16" s="60" t="inlineStr">
         <is>
-          <t>本機ステージング（最大 2 ファイル）</t>
+          <t>有無</t>
         </is>
       </c>
       <c r="F16" s="60" t="inlineStr">
         <is>
-          <t>両方取れない場合は ER-004。当日0件は判定へ（ER-012）</t>
+          <t>両方無しは ER-004</t>
         </is>
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>Hinemos 起動 Layer①（24/25 共通）</t>
+          <t>空ファイル</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>共通 1 ジョブ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="84" customHeight="1" s="65">
-      <c r="B17" s="60" t="n">
-        <v>20</v>
+          <t>24/25 共通</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="65">
+      <c r="B17" s="60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C17" s="60" t="inlineStr">
         <is>
-          <t>採用判定。当日ファイルが指定時刻（TBD-19、例 6:00）までに作成済 → 当日を採用。障害、または当日未作成 → 昨日作成の翌日以降を採用。2 本を後勝ちで重ねない</t>
+          <t>gz を取得</t>
         </is>
       </c>
       <c r="D17" s="60" t="inlineStr">
         <is>
-          <t>ステージング上の当日 ＋ 昨日の翌日以降</t>
+          <t>連携用GCS</t>
         </is>
       </c>
       <c r="E17" s="60" t="inlineStr">
         <is>
-          <t>採用する 1 ファイル</t>
+          <t>gz（最大2）</t>
         </is>
       </c>
       <c r="F17" s="60" t="inlineStr">
         <is>
-          <t>当日未作成・障害は ER-012 で昨日分を採用。昨日分も無ければ中断</t>
+          <t>失敗は ER-004</t>
         </is>
       </c>
       <c r="G17" s="60" t="inlineStr">
         <is>
-          <t>TBD-13/19。後勝ちしない</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>判定は本機。自動発注側では選ばない</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="72" customHeight="1" s="65">
-      <c r="B18" s="60" t="n">
-        <v>30</v>
+          <t>当日 kankoku_*.gz と昨日 subkankoku_*.gz</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="65">
+      <c r="B18" s="60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="C18" s="60" t="inlineStr">
         <is>
-          <t>採用した 1 本を SIREJAN_RCMDORDER_LAST へ変換。数量は×1000しない。発注単位の整数倍であれば発注バラ数を直接設定（倍数に丸めない）。Ordertype は勧告ファイルの西友中分類（西友ライン＝部門）を部門CDとし、自動発注GCS JIHA.BUMON_ZONE（部門CD, ZONECD）→ JIHA.ZONE_LOGIC（ZONECD, 論理区分）。論理区分 01→0（非日配）、02→1（日配）、03→1（生鮮）。TRIAL 商品マスタは参照しない。</t>
+          <t>gz を展開</t>
         </is>
       </c>
       <c r="D18" s="60" t="inlineStr">
         <is>
-          <t>採用した 1 本（部門＝西友中分類／西友ライン）＋ JIHA.BUMON_ZONE / JIHA.ZONE_LOGIC（自動発注GCS）</t>
+          <t>gz</t>
         </is>
       </c>
       <c r="E18" s="60" t="inlineStr">
         <is>
-          <t>7項目ファイル 1 本</t>
-        </is>
-      </c>
-      <c r="F18" s="60" t="inlineStr">
-        <is>
-          <t>必須項目欠落・桁超過は ER-005。未確定項目は TBD のまま</t>
-        </is>
-      </c>
+          <t>ステージング</t>
+        </is>
+      </c>
+      <c r="F18" s="60" t="n"/>
       <c r="G18" s="60" t="inlineStr">
         <is>
-          <t>R01/R04/R06/R07 確定。部門は勧告ファイル。商品マスタは見ない。数量は発注単位の整数倍。店・仕入先・商品はマスタ統合に追随</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>変換対象は採用した 1 本のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="21.75" customHeight="1" s="65">
-      <c r="B19" s="60" t="n">
-        <v>40</v>
+          <t>最大 2 ファイル</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="65">
+      <c r="B19" s="60" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="C19" s="60" t="inlineStr">
         <is>
-          <t>変換後ファイル（採用した 1 本）を TRIAL 自動発注GCSへアップロード</t>
+          <t>採用する 1 本を決める</t>
         </is>
       </c>
       <c r="D19" s="60" t="inlineStr">
         <is>
-          <t>7項目ファイル 1 本</t>
+          <t>ステージング</t>
         </is>
       </c>
       <c r="E19" s="60" t="inlineStr">
         <is>
+          <t>採用 1 本</t>
+        </is>
+      </c>
+      <c r="F19" s="60" t="inlineStr">
+        <is>
+          <t>当日無しは ER-012。昨日も無しは中断</t>
+        </is>
+      </c>
+      <c r="G19" s="60" t="inlineStr">
+        <is>
+          <t>締切 TBD-19（例 6:00）。2本は重ねない</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>判定は本機</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="65">
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="inlineStr">
+        <is>
+          <t>店CDを統合マスタ後へ</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="inlineStr">
+        <is>
+          <t>採用 1 本</t>
+        </is>
+      </c>
+      <c r="E20" s="60" t="inlineStr">
+        <is>
+          <t>店舗CD</t>
+        </is>
+      </c>
+      <c r="F20" s="60" t="inlineStr">
+        <is>
+          <t>不一致は ER-005</t>
+        </is>
+      </c>
+      <c r="G20" s="60" t="inlineStr">
+        <is>
+          <t>切捨てなし。TBD-01</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="65">
+      <c r="B21" s="60" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C21" s="60" t="inlineStr">
+        <is>
+          <t>商品CDを統合マスタ後へ</t>
+        </is>
+      </c>
+      <c r="D21" s="60" t="inlineStr">
+        <is>
+          <t>採用 1 本</t>
+        </is>
+      </c>
+      <c r="E21" s="60" t="inlineStr">
+        <is>
+          <t>仕入発注JAN</t>
+        </is>
+      </c>
+      <c r="F21" s="60" t="inlineStr">
+        <is>
+          <t>不一致は ER-005</t>
+        </is>
+      </c>
+      <c r="G21" s="60" t="inlineStr">
+        <is>
+          <t>独自変換なし</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="65">
+      <c r="B22" s="60" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C22" s="60" t="inlineStr">
+        <is>
+          <t>仕入先CDを統合マスタ後へ</t>
+        </is>
+      </c>
+      <c r="D22" s="60" t="inlineStr">
+        <is>
+          <t>採用 1 本</t>
+        </is>
+      </c>
+      <c r="E22" s="60" t="inlineStr">
+        <is>
+          <t>ベンダーCD</t>
+        </is>
+      </c>
+      <c r="F22" s="60" t="inlineStr">
+        <is>
+          <t>不一致は ER-005</t>
+        </is>
+      </c>
+      <c r="G22" s="60" t="inlineStr">
+        <is>
+          <t>切捨てなし。TBD-08</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="65">
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>数量を設定</t>
+        </is>
+      </c>
+      <c r="D23" s="60" t="inlineStr">
+        <is>
+          <t>発注バラ数</t>
+        </is>
+      </c>
+      <c r="E23" s="60" t="inlineStr">
+        <is>
+          <t>推奨発注数量</t>
+        </is>
+      </c>
+      <c r="F23" s="60" t="inlineStr">
+        <is>
+          <t>整数倍でないは ER-005</t>
+        </is>
+      </c>
+      <c r="G23" s="60" t="inlineStr">
+        <is>
+          <t>×1000しない。丸めない</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="65">
+      <c r="B24" s="60" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C24" s="60" t="inlineStr">
+        <is>
+          <t>納品日を移す</t>
+        </is>
+      </c>
+      <c r="D24" s="60" t="inlineStr">
+        <is>
+          <t>納品日</t>
+        </is>
+      </c>
+      <c r="E24" s="60" t="inlineStr">
+        <is>
+          <t>ShippingDate</t>
+        </is>
+      </c>
+      <c r="F24" s="60" t="n"/>
+      <c r="G24" s="60" t="inlineStr">
+        <is>
+          <t>yyyymmdd のまま</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="65">
+      <c r="B25" s="60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C25" s="60" t="inlineStr">
+        <is>
+          <t>部門CDを取る</t>
+        </is>
+      </c>
+      <c r="D25" s="60" t="inlineStr">
+        <is>
+          <t>勧告ファイルの西友中分類</t>
+        </is>
+      </c>
+      <c r="E25" s="60" t="inlineStr">
+        <is>
+          <t>部門CD</t>
+        </is>
+      </c>
+      <c r="F25" s="60" t="n"/>
+      <c r="G25" s="60" t="inlineStr">
+        <is>
+          <t>西友ライン＝部門。商品マスタは見ない</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="65">
+      <c r="B26" s="60" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C26" s="60" t="inlineStr">
+        <is>
+          <t>JIHA.BUMON_ZONE を引く</t>
+        </is>
+      </c>
+      <c r="D26" s="60" t="inlineStr">
+        <is>
+          <t>自動発注GCS / JIHA.BUMON_ZONE</t>
+        </is>
+      </c>
+      <c r="E26" s="60" t="inlineStr">
+        <is>
+          <t>ZONECD</t>
+        </is>
+      </c>
+      <c r="F26" s="60" t="inlineStr">
+        <is>
+          <t>部門CDが無いのは ER-007</t>
+        </is>
+      </c>
+      <c r="G26" s="60" t="inlineStr">
+        <is>
+          <t>キーは部門CD。参照のみ。書かない</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>自動発注GCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="65">
+      <c r="B27" s="60" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C27" s="60" t="inlineStr">
+        <is>
+          <t>JIHA.ZONE_LOGIC を引く</t>
+        </is>
+      </c>
+      <c r="D27" s="60" t="inlineStr">
+        <is>
+          <t>自動発注GCS / JIHA.ZONE_LOGIC</t>
+        </is>
+      </c>
+      <c r="E27" s="60" t="inlineStr">
+        <is>
+          <t>論理区分</t>
+        </is>
+      </c>
+      <c r="F27" s="60" t="inlineStr">
+        <is>
+          <t>引けないは ER-007</t>
+        </is>
+      </c>
+      <c r="G27" s="60" t="inlineStr">
+        <is>
+          <t>キーは ZONECD。参照のみ。書かない</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>自動発注GCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="65">
+      <c r="B28" s="60" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C28" s="60" t="inlineStr">
+        <is>
+          <t>Ordertype を設定</t>
+        </is>
+      </c>
+      <c r="D28" s="60" t="inlineStr">
+        <is>
+          <t>論理区分</t>
+        </is>
+      </c>
+      <c r="E28" s="60" t="inlineStr">
+        <is>
+          <t>Ordertype</t>
+        </is>
+      </c>
+      <c r="F28" s="60" t="inlineStr">
+        <is>
+          <t>01/02/03 以外は ER-007</t>
+        </is>
+      </c>
+      <c r="G28" s="60" t="inlineStr">
+        <is>
+          <t>01→0、02→1、03→1</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="65">
+      <c r="B29" s="60" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C29" s="60" t="inlineStr">
+        <is>
+          <t>更新日を設定</t>
+        </is>
+      </c>
+      <c r="D29" s="60" t="inlineStr">
+        <is>
+          <t>発注日（候補）</t>
+        </is>
+      </c>
+      <c r="E29" s="60" t="inlineStr">
+        <is>
+          <t>更新日</t>
+        </is>
+      </c>
+      <c r="F29" s="60" t="n"/>
+      <c r="G29" s="60" t="inlineStr">
+        <is>
+          <t>TBD-10</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="65">
+      <c r="B30" s="60" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C30" s="60" t="inlineStr">
+        <is>
+          <t>SIREJAN を書く</t>
+        </is>
+      </c>
+      <c r="D30" s="60" t="inlineStr">
+        <is>
+          <t>7項目</t>
+        </is>
+      </c>
+      <c r="E30" s="60" t="inlineStr">
+        <is>
+          <t>1 ファイル</t>
+        </is>
+      </c>
+      <c r="F30" s="60" t="inlineStr">
+        <is>
+          <t>必須欠落は ER-005</t>
+        </is>
+      </c>
+      <c r="G30" s="60" t="inlineStr">
+        <is>
+          <t>gz ではない</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>SIREJAN_RCMDORDER_LAST_YYYYMMDDhhmmss</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="65">
+      <c r="B31" s="60" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C31" s="60" t="inlineStr">
+        <is>
+          <t>自動発注GCSへ置く</t>
+        </is>
+      </c>
+      <c r="D31" s="60" t="inlineStr">
+        <is>
+          <t>1 ファイル</t>
+        </is>
+      </c>
+      <c r="E31" s="60" t="inlineStr">
+        <is>
           <t>gs://{TBD-06}/</t>
         </is>
       </c>
-      <c r="F19" s="60" t="inlineStr">
-        <is>
-          <t>配置失敗は ER-006 で中断</t>
-        </is>
-      </c>
-      <c r="G19" s="60" t="inlineStr">
-        <is>
-          <t>OrdreSV へは既存自動発注転送。本STEPの外</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="F31" s="60" t="inlineStr">
+        <is>
+          <t>失敗は ER-006</t>
+        </is>
+      </c>
+      <c r="G31" s="60" t="inlineStr">
+        <is>
+          <t>OrdreSV は本STEPの外</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>出力は常に 1 本</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="21.75" customHeight="1" s="65">
-      <c r="B20" s="58" t="n"/>
-      <c r="C20" s="58" t="n"/>
-      <c r="D20" s="58" t="n"/>
-      <c r="E20" s="58" t="n"/>
-      <c r="F20" s="58" t="n"/>
-      <c r="G20" s="58" t="n"/>
-    </row>
-    <row r="21" ht="21.75" customHeight="1" s="65">
-      <c r="B21" s="58" t="n"/>
-      <c r="C21" s="58" t="n"/>
-      <c r="D21" s="58" t="n"/>
-      <c r="E21" s="58" t="n"/>
-      <c r="F21" s="58" t="n"/>
-      <c r="G21" s="58" t="n"/>
-    </row>
-    <row r="22" ht="21.75" customHeight="1" s="65">
-      <c r="B22" s="58" t="n"/>
-      <c r="C22" s="58" t="n"/>
-      <c r="D22" s="58" t="n"/>
-      <c r="E22" s="58" t="n"/>
-      <c r="F22" s="58" t="n"/>
-      <c r="G22" s="58" t="n"/>
-    </row>
-    <row r="23" ht="21.75" customHeight="1" s="65">
-      <c r="B23" s="58" t="n"/>
-      <c r="C23" s="58" t="n"/>
-      <c r="D23" s="58" t="n"/>
-      <c r="E23" s="58" t="n"/>
-      <c r="F23" s="58" t="n"/>
-      <c r="G23" s="58" t="n"/>
-    </row>
-    <row r="24" ht="21.75" customHeight="1" s="65">
-      <c r="B24" s="58" t="n"/>
-      <c r="C24" s="58" t="n"/>
-      <c r="D24" s="58" t="n"/>
-      <c r="E24" s="58" t="n"/>
-      <c r="F24" s="58" t="n"/>
-      <c r="G24" s="58" t="n"/>
-    </row>
-    <row r="25" ht="21.75" customHeight="1" s="65">
-      <c r="B25" s="58" t="n"/>
-      <c r="C25" s="58" t="n"/>
-      <c r="D25" s="58" t="n"/>
-      <c r="E25" s="58" t="n"/>
-      <c r="F25" s="58" t="n"/>
-      <c r="G25" s="58" t="n"/>
-    </row>
-    <row r="26" ht="21.75" customHeight="1" s="65">
-      <c r="B26" s="58" t="n"/>
-      <c r="C26" s="58" t="n"/>
-      <c r="D26" s="58" t="n"/>
-      <c r="E26" s="58" t="n"/>
-      <c r="F26" s="58" t="n"/>
-      <c r="G26" s="58" t="n"/>
-    </row>
-    <row r="27" ht="21.75" customHeight="1" s="65">
-      <c r="B27" s="58" t="n"/>
-      <c r="C27" s="58" t="n"/>
-      <c r="D27" s="58" t="n"/>
-      <c r="E27" s="58" t="n"/>
-      <c r="F27" s="58" t="n"/>
-      <c r="G27" s="58" t="n"/>
-    </row>
-    <row r="28" ht="21.75" customHeight="1" s="65">
-      <c r="B28" s="58" t="n"/>
-      <c r="C28" s="58" t="n"/>
-      <c r="D28" s="58" t="n"/>
-      <c r="E28" s="58" t="n"/>
-      <c r="F28" s="58" t="n"/>
-      <c r="G28" s="58" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" s="65">
-      <c r="B29" s="58" t="n"/>
-      <c r="C29" s="58" t="n"/>
-      <c r="D29" s="58" t="n"/>
-      <c r="E29" s="58" t="n"/>
-      <c r="F29" s="58" t="n"/>
-      <c r="G29" s="58" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1" s="65"/>
-    <row r="31" ht="18" customHeight="1" s="65">
-      <c r="B31" s="43" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="65">
       <c r="B32" s="44" t="n"/>
@@ -14468,13 +14780,15 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="60" t="n">
-        <v>10</v>
+    <row r="14" ht="18" customHeight="1" s="65">
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C14" s="60" t="inlineStr">
         <is>
-          <t>Sinops から当日勧告を取得</t>
+          <t>当日勧告を取得</t>
         </is>
       </c>
       <c r="D14" s="60" t="inlineStr">
@@ -14484,61 +14798,107 @@
       </c>
       <c r="E14" s="60" t="inlineStr">
         <is>
-          <t>DSS 作業領域</t>
+          <t>DSS作業領域</t>
         </is>
       </c>
       <c r="F14" s="60" t="inlineStr">
         <is>
-          <t>取得失敗は処理中断・通知</t>
+          <t>失敗は中断・通知</t>
         </is>
       </c>
       <c r="G14" s="48" t="n"/>
     </row>
-    <row r="15" ht="21.75" customHeight="1" s="65">
-      <c r="B15" s="60" t="n">
-        <v>20</v>
+    <row r="15" ht="18" customHeight="1" s="65">
+      <c r="B15" s="60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>連携用GCSへ gz を置く。続けて空の kankoku.end</t>
+          <t>gz にする</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr">
         <is>
-          <t>DSS 作業領域</t>
+          <t>DSS作業領域</t>
         </is>
       </c>
       <c r="E15" s="60" t="inlineStr">
         <is>
+          <t>kankoku_YYYYMMDDhhmmss.gz</t>
+        </is>
+      </c>
+      <c r="F15" s="60" t="n"/>
+      <c r="G15" s="48" t="inlineStr">
+        <is>
+          <t>論理 kankoku.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="65">
+      <c r="B16" s="60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>gz を連携用GCSへ置く</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="inlineStr">
+        <is>
+          <t>gz</t>
+        </is>
+      </c>
+      <c r="E16" s="60" t="inlineStr">
+        <is>
           <t>gs://ods-seiyu-prod/{TBD-05}/</t>
         </is>
       </c>
-      <c r="F15" s="60" t="inlineStr">
-        <is>
-          <t>配置失敗は処理中断・通知</t>
-        </is>
-      </c>
-      <c r="G15" s="60" t="inlineStr">
-        <is>
-          <t>UTF-8。フォルダ名は西友 from_to_連番（TBD-05）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21.75" customHeight="1" s="65">
-      <c r="B16" s="58" t="n"/>
-      <c r="C16" s="58" t="n"/>
-      <c r="D16" s="58" t="n"/>
-      <c r="E16" s="58" t="n"/>
-      <c r="F16" s="58" t="n"/>
-      <c r="G16" s="58" t="n"/>
-    </row>
-    <row r="17" ht="21.75" customHeight="1" s="65">
-      <c r="B17" s="58" t="n"/>
-      <c r="C17" s="58" t="n"/>
-      <c r="D17" s="58" t="n"/>
-      <c r="E17" s="58" t="n"/>
-      <c r="F17" s="58" t="n"/>
-      <c r="G17" s="58" t="n"/>
+      <c r="F16" s="60" t="inlineStr">
+        <is>
+          <t>失敗は中断・通知</t>
+        </is>
+      </c>
+      <c r="G16" s="48" t="inlineStr">
+        <is>
+          <t>from_to_連番（TBD-05）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="65">
+      <c r="B17" s="60" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="inlineStr">
+        <is>
+          <t>空の kankoku.end を置く</t>
+        </is>
+      </c>
+      <c r="D17" s="60" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E17" s="60" t="inlineStr">
+        <is>
+          <t>kankoku.end</t>
+        </is>
+      </c>
+      <c r="F17" s="60" t="inlineStr">
+        <is>
+          <t>失敗は中断・通知</t>
+        </is>
+      </c>
+      <c r="G17" s="48" t="inlineStr">
+        <is>
+          <t>gz の後</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="65">
       <c r="B18" s="58" t="n"/>
